--- a/quizzes/sculpture-17e-niveau1.xlsx
+++ b/quizzes/sculpture-17e-niveau1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE615FA-60A2-4C45-83D3-B24FAF16A27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C9B8CA-AFE2-49E9-B10D-1B6C4361CE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9555" yWindow="195" windowWidth="17580" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz sculpture 17e" sheetId="1" r:id="rId1"/>
@@ -921,325 +921,325 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
+      <c r="A3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>19</v>
+      <c r="A4" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>23</v>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>31</v>
+      <c r="A7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>128</v>
+        <v>141</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>37</v>
+      <c r="A9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>41</v>
+        <v>133</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>49</v>
+        <v>143</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>135</v>
+      <c r="A13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>72</v>
+      <c r="E18" s="8" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C20" s="7">
         <v>1670</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1261,205 +1261,208 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>92</v>
+      <c r="A23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>93</v>
+      <c r="A24" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>109</v>
+      <c r="A27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>114</v>
+      <c r="A28" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
-        <v>115</v>
+      <c r="A29" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A14" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A15" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A20" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A22" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="A24" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="A29" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A30" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A8" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Christian_IV_of_Denmark_by_Karel_Van_Mander_III%2C_1640%2C_with_carvings_by_Grinling_Gibbons_-_King%27s_Eating_Room_-_Hampton_Court_Palace_-_London%2C_UK_-_DSC07092.jpg/960px-Christian_IV_of_Denmark_by_Karel_Van_Mander_III%2C_1640%2C_with_carvings_by_Grinling_Gibbons_-_King%27s_Eating_Room_-_Hampton_Court_Palace_-_London%2C_UK_-_DSC07092.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F3E7F41-26BF-458A-94B1-213430A1F783}"/>
-    <hyperlink ref="A10" r:id="rId18" xr:uid="{C2DC1B92-9770-486E-9EF7-10599797CA4B}"/>
-    <hyperlink ref="A19" r:id="rId19" xr:uid="{3B324DEE-1986-4872-B8E4-0C4FA38253F7}"/>
-    <hyperlink ref="A5" r:id="rId20" xr:uid="{CB42134D-555E-4F62-8CAF-A7A1D8D7A524}"/>
-    <hyperlink ref="A12" r:id="rId21" xr:uid="{D9587983-061D-4196-AB1D-E1032241541C}"/>
-    <hyperlink ref="A13" r:id="rId22" xr:uid="{23A40C34-B762-48F6-89DF-6501B6134606}"/>
-    <hyperlink ref="A23" r:id="rId23" xr:uid="{DA5980D4-FED8-4799-944C-BBD25DC845CD}"/>
-    <hyperlink ref="A27" r:id="rId24" xr:uid="{80F42E70-5E3B-4F20-B583-82AFDAE47485}"/>
-    <hyperlink ref="A31" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Jean_Warin_%28Lie%C4%9Do%2C_1607_-_Parizo%2C_1672%29._Portreto_de_Ludoviko_XIV%2C_re%C4%9Do_de_Francio_%281638-1715%29._1665-1666._Busto%2C_marmoro._Versajlo%2C_Nacia_Muzeo_de_la_kasteloj_de_Versajlo_kaj_Trianon%2C_MV_494.jpg/1280px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8D58745C-8109-4D9B-B46F-39F6AAF3D827}"/>
-    <hyperlink ref="A7" r:id="rId26" xr:uid="{B659B029-E3F3-4F6A-8EEC-3BE45DADAF4A}"/>
-    <hyperlink ref="A9" r:id="rId27" xr:uid="{86FA17D8-46DD-49B9-B31E-EE9E1743213D}"/>
-    <hyperlink ref="A16" r:id="rId28" xr:uid="{7C938100-D260-4A0E-8561-FE54B930C5BB}"/>
-    <hyperlink ref="A17" r:id="rId29" xr:uid="{156922ED-4535-4392-B455-2CF759656119}"/>
+    <hyperlink ref="A14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A11" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A30" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A25" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A17" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A23" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A22" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="A9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A27" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A16" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Christian_IV_of_Denmark_by_Karel_Van_Mander_III%2C_1640%2C_with_carvings_by_Grinling_Gibbons_-_King%27s_Eating_Room_-_Hampton_Court_Palace_-_London%2C_UK_-_DSC07092.jpg/960px-Christian_IV_of_Denmark_by_Karel_Van_Mander_III%2C_1640%2C_with_carvings_by_Grinling_Gibbons_-_King%27s_Eating_Room_-_Hampton_Court_Palace_-_London%2C_UK_-_DSC07092.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F3E7F41-26BF-458A-94B1-213430A1F783}"/>
+    <hyperlink ref="A24" r:id="rId18" xr:uid="{C2DC1B92-9770-486E-9EF7-10599797CA4B}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{3B324DEE-1986-4872-B8E4-0C4FA38253F7}"/>
+    <hyperlink ref="A28" r:id="rId20" xr:uid="{CB42134D-555E-4F62-8CAF-A7A1D8D7A524}"/>
+    <hyperlink ref="A10" r:id="rId21" xr:uid="{D9587983-061D-4196-AB1D-E1032241541C}"/>
+    <hyperlink ref="A29" r:id="rId22" xr:uid="{23A40C34-B762-48F6-89DF-6501B6134606}"/>
+    <hyperlink ref="A3" r:id="rId23" xr:uid="{DA5980D4-FED8-4799-944C-BBD25DC845CD}"/>
+    <hyperlink ref="A31" r:id="rId24" xr:uid="{80F42E70-5E3B-4F20-B583-82AFDAE47485}"/>
+    <hyperlink ref="A18" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Jean_Warin_%28Lie%C4%9Do%2C_1607_-_Parizo%2C_1672%29._Portreto_de_Ludoviko_XIV%2C_re%C4%9Do_de_Francio_%281638-1715%29._1665-1666._Busto%2C_marmoro._Versajlo%2C_Nacia_Muzeo_de_la_kasteloj_de_Versajlo_kaj_Trianon%2C_MV_494.jpg/1280px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8D58745C-8109-4D9B-B46F-39F6AAF3D827}"/>
+    <hyperlink ref="A4" r:id="rId26" xr:uid="{B659B029-E3F3-4F6A-8EEC-3BE45DADAF4A}"/>
+    <hyperlink ref="A8" r:id="rId27" xr:uid="{86FA17D8-46DD-49B9-B31E-EE9E1743213D}"/>
+    <hyperlink ref="A19" r:id="rId28" xr:uid="{7C938100-D260-4A0E-8561-FE54B930C5BB}"/>
+    <hyperlink ref="A12" r:id="rId29" xr:uid="{156922ED-4535-4392-B455-2CF759656119}"/>
     <hyperlink ref="A21" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/Cristo_de_la_Clemencia%2C_obra_de_Juan_Mart%C3%ADnez_Montan%C3%A9s%2C_data_de_1604_o_1605.jpg/1280px-Cristo_de_la_Clemencia%2C_obra_de_Juan_Mart%C3%ADnez_Montan%C3%A9s%2C_data_de_1604_o_1605.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7CADC0D8-404A-4EFB-B116-DCFBD2122906}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
